--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace_huaxia\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20496" windowHeight="7752"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="bz">填写说明!$A$143:$A$320</definedName>
     <definedName name="gmd">填写说明!$A$7:$A$46</definedName>
-    <definedName name="qd">填写说明!$A$323:$A$329</definedName>
+    <definedName name="qd">填写说明!$A$323:$A$331</definedName>
     <definedName name="ywzl">填写说明!$A$89:$A$104</definedName>
     <definedName name="关联账户所在地">填写说明!$A$7:$A$46</definedName>
   </definedNames>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="330">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -134,6 +134,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
@@ -1062,6 +1063,64 @@
     <t>**产品代码</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
+  <si>
+    <t>**交易序列号</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>**关联活期存款账号开户行代码</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>**关联活期存款账号开户行名称</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 银联交易</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 第三方支付</t>
+    </r>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1070,7 +1129,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00000_ "/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1080,6 +1139,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1094,12 +1154,14 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1155,6 +1217,7 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1300,7 +1363,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1415,6 +1478,9 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1764,30 +1830,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AH2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.75" style="32" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="22.69921875" style="32" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="18" style="32" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.125" style="32" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.125" style="32" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="18.5" style="32" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.125" style="32" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="30" style="32" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="34.625" style="38" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="24" style="32" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="15.5" style="32" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.875" style="32" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="28" max="29" width="18" style="31" customWidth="1"/>
-    <col min="30" max="30" width="9" style="33" collapsed="1"/>
-    <col min="31" max="31" width="9" style="33"/>
-    <col min="32" max="16384" width="9" style="33" collapsed="1"/>
+    <col min="3" max="9" width="26.09765625" style="32" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="30.59765625" style="32" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="31.3984375" style="32" customWidth="1" collapsed="1"/>
+    <col min="12" max="17" width="26.09765625" style="32" customWidth="1" collapsed="1"/>
+    <col min="18" max="19" width="19.3984375" style="32" customWidth="1" collapsed="1"/>
+    <col min="20" max="21" width="26.09765625" style="32" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="18.5" style="32" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="26.09765625" style="32" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="18.3984375" style="32" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="30" style="32" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="34.59765625" style="38" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="24" style="32" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="15.5" style="32" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="16.8984375" style="32" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="17.3984375" style="32" customWidth="1" collapsed="1"/>
+    <col min="31" max="32" width="18" style="31" customWidth="1"/>
+    <col min="33" max="33" width="9" style="33" collapsed="1"/>
+    <col min="34" max="34" width="9" style="33"/>
+    <col min="35" max="16384" width="9" style="33" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="28" customFormat="1">
+    <row r="1" spans="1:32" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -1810,73 +1879,82 @@
         <v>6</v>
       </c>
       <c r="H1" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="I1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="J1" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="L1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="M1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="N1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="O1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="P1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="Q1" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="R1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="S1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="T1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="U1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="V1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="W1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="X1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="Y1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="36" t="s">
+      <c r="Z1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="29" t="s">
+      <c r="AA1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="29" t="s">
+      <c r="AB1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="29" t="s">
+      <c r="AC1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="29" t="s">
+      <c r="AD1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="30" t="s">
+      <c r="AE1" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="AC1" s="30" t="s">
+      <c r="AF1" s="30" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="35" customFormat="1">
+    <row r="2" spans="1:32" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34"/>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -1899,25 +1977,28 @@
       <c r="T2" s="34"/>
       <c r="U2" s="34"/>
       <c r="V2" s="34"/>
-      <c r="W2" s="37"/>
+      <c r="W2" s="34"/>
       <c r="X2" s="34"/>
       <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
+      <c r="Z2" s="37"/>
       <c r="AA2" s="34"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
+      <c r="AB2" s="34"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1 M1 O1:P1 S1 Y1"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:M1 P1 R1:S1 V1 AB1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>bz</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>ywzl</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>qd</formula1>
     </dataValidation>
   </dataValidations>
@@ -1930,25 +2011,25 @@
           <x14:formula1>
             <xm:f>填写说明!$A$7:$A$46</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
+          <xm:sqref>L2:L1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$48:$A$49</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
+          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$51:$A$87</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
+          <xm:sqref>P2:P1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$106:$A$141</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
+          <xm:sqref>S2:S1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1958,1647 +2039,1657 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A329"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:A331"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="73.3984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="30">
+    <row r="2" spans="1:1" ht="31.8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" ht="15.75">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="19" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="19" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="19" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="19" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="19" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="19" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="19" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="19" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="19" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="19" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="20" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="20" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="20" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="20" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="20" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="20" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="20" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="20" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="20" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="20" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="20" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="20" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="20" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="185" spans="1:1">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="20" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="20" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="187" spans="1:1">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="20" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="188" spans="1:1">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="20" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="189" spans="1:1">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="20" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="190" spans="1:1">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="20" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="191" spans="1:1">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="20" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="192" spans="1:1">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="20" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="193" spans="1:1">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="194" spans="1:1">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="195" spans="1:1">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="196" spans="1:1">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="20" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="197" spans="1:1">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="20" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="198" spans="1:1">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="20" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="199" spans="1:1">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="20" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="200" spans="1:1">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="20" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="201" spans="1:1">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="20" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="202" spans="1:1">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="20" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="203" spans="1:1">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="204" spans="1:1">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="20" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="205" spans="1:1">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="20" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="206" spans="1:1">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="20" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="207" spans="1:1">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="20" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="208" spans="1:1">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="20" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="209" spans="1:1">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="210" spans="1:1">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="20" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="211" spans="1:1">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="20" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="212" spans="1:1">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="20" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="213" spans="1:1">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="20" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="214" spans="1:1">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="20" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="215" spans="1:1">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="20" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="216" spans="1:1">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="217" spans="1:1">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="20" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="218" spans="1:1">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="20" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="219" spans="1:1">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="20" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="220" spans="1:1">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="20" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="221" spans="1:1">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="20" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="222" spans="1:1">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="20" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="223" spans="1:1">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="20" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="224" spans="1:1">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="20" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="225" spans="1:1">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="20" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="226" spans="1:1">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="20" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="227" spans="1:1">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="20" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="228" spans="1:1">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="20" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="229" spans="1:1">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="20" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="230" spans="1:1">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="20" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="231" spans="1:1">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="20" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="232" spans="1:1">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="20" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="233" spans="1:1">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="20" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="234" spans="1:1">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="20" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="235" spans="1:1">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="20" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="236" spans="1:1">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="20" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="237" spans="1:1">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="20" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="238" spans="1:1">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="20" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="239" spans="1:1">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="20" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="240" spans="1:1">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="20" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="241" spans="1:1">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="20" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="242" spans="1:1">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="20" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="243" spans="1:1">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="20" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="244" spans="1:1">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="20" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="245" spans="1:1">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="20" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="246" spans="1:1">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="20" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="247" spans="1:1">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="20" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="248" spans="1:1">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="20" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="249" spans="1:1">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="20" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="250" spans="1:1">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="20" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="251" spans="1:1">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="20" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="252" spans="1:1">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="20" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="253" spans="1:1">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="20" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="254" spans="1:1">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="20" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="255" spans="1:1">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="20" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="256" spans="1:1">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="20" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="257" spans="1:1">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="20" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="258" spans="1:1">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="20" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="259" spans="1:1">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="20" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="260" spans="1:1">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="20" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="261" spans="1:1">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="20" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="262" spans="1:1">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="20" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="263" spans="1:1">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="20" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="264" spans="1:1">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="20" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="265" spans="1:1">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="20" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="266" spans="1:1">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="20" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="267" spans="1:1">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="20" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="268" spans="1:1">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="20" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="269" spans="1:1">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="20" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="270" spans="1:1">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="20" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="271" spans="1:1">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="20" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="272" spans="1:1">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="20" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="273" spans="1:1">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="20" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="274" spans="1:1">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="20" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="275" spans="1:1">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="20" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="276" spans="1:1">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="20" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="277" spans="1:1">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="20" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="278" spans="1:1">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="20" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="279" spans="1:1">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="20" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="280" spans="1:1">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="20" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="281" spans="1:1">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="20" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="282" spans="1:1">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="20" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="283" spans="1:1">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="20" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="284" spans="1:1">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="20" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="285" spans="1:1">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="20" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="286" spans="1:1">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="20" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="287" spans="1:1">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="20" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="288" spans="1:1">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="20" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="289" spans="1:1">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="20" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="290" spans="1:1">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="20" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="291" spans="1:1">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="20" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="292" spans="1:1">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="20" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="293" spans="1:1">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="20" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="294" spans="1:1">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="20" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="295" spans="1:1">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="20" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="296" spans="1:1">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="20" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:1">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="20" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="298" spans="1:1">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="20" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="299" spans="1:1">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="20" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="300" spans="1:1">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="20" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="301" spans="1:1">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="20" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="302" spans="1:1">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="20" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="303" spans="1:1">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="20" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="304" spans="1:1">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" s="20" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="305" spans="1:1">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" s="20" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="306" spans="1:1">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" s="20" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="307" spans="1:1">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" s="20" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="308" spans="1:1">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" s="20" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="309" spans="1:1">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" s="20" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="310" spans="1:1">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" s="20" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="311" spans="1:1">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" s="20" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="312" spans="1:1">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" s="20" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="313" spans="1:1">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" s="20" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="314" spans="1:1">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" s="20" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="315" spans="1:1">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" s="20" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="316" spans="1:1">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" s="20" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="317" spans="1:1">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" s="20" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="318" spans="1:1">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" s="20" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="319" spans="1:1">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" s="20" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="320" spans="1:1">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" s="22" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="23" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="24" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="25" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="26" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="26" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="26" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="329" spans="1:1">
-      <c r="A329" s="27" t="s">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="39" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="39" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="27" t="s">
         <v>316</v>
       </c>
     </row>
@@ -3612,13 +3703,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>317</v>
       </c>
@@ -3626,7 +3717,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>319</v>
       </c>
@@ -3634,7 +3725,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29.1" customHeight="1">
+    <row r="3" spans="1:2" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>320</v>
       </c>
